--- a/output/pdf_financials_xlsx/ALA.xlsx
+++ b/output/pdf_financials_xlsx/ALA.xlsx
@@ -3174,55 +3174,55 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.103571</v>
+        <v>0.007505</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.064439</v>
+        <v>0.005587</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.101859</v>
+        <v>0.008642</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.11859</v>
+        <v>0.021456</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>8.189999999999997e-05</v>
+        <v>3.32e-05</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.0001297</v>
+        <v>4.19e-05</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.0005404</v>
+        <v>4.829999999999999e-05</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.0004986</v>
+        <v>4.28e-05</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.0004735</v>
+        <v>3.6e-05</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.0034155</v>
+        <v>0.0001999</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.0016335</v>
+        <v>0.0002802</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.001829</v>
+        <v>0.000234</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.001779</v>
+        <v>0.000188</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.003525</v>
+        <v>0.000169</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.002103</v>
+        <v>0.000147</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.002058</v>
+        <v>0.000175</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.002175</v>
+        <v>0.000188</v>
       </c>
     </row>
     <row r="49">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -16484,7 +16484,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -19798,7 +19798,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -25162,7 +25162,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -36073,7 +36073,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E280" s="5" t="n">

--- a/output/pdf_financials_xlsx/ALA.xlsx
+++ b/output/pdf_financials_xlsx/ALA.xlsx
@@ -3174,55 +3174,55 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.007505</v>
+        <v>0.103571</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.005587</v>
+        <v>0.064439</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.008642</v>
+        <v>0.101859</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.021456</v>
+        <v>0.11859</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>3.32e-05</v>
+        <v>8.189999999999997e-05</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>4.19e-05</v>
+        <v>0.0001297</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>4.829999999999999e-05</v>
+        <v>0.0005404</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>4.28e-05</v>
+        <v>0.0004986</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>3.6e-05</v>
+        <v>0.0004735</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.0001999</v>
+        <v>0.0034155</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.0002802</v>
+        <v>0.0016335</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.000234</v>
+        <v>0.001829</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.000188</v>
+        <v>0.001779</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.000169</v>
+        <v>0.003525</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.000147</v>
+        <v>0.002103</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.000175</v>
+        <v>0.002058</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.000188</v>
+        <v>0.002175</v>
       </c>
     </row>
     <row r="49">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -16484,7 +16484,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -19798,7 +19798,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -25162,7 +25162,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -36073,7 +36073,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E280" s="5" t="n">
@@ -67374,7 +67374,7 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
